--- a/survey_templates/033_resume_review_questionnaire--survey_templates.xlsx
+++ b/survey_templates/033_resume_review_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'chronological'}</t>
+          <t>chronological</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Chronological'}</t>
+          <t>Chronological</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'functional'}</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Functional'}</t>
+          <t>Functional</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'field'}</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Field'}</t>
+          <t>Field</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_looking'}</t>
+          <t>not_looking</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not looking'}</t>
+          <t>Not looking</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Entry Level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Mid-level'}</t>
+          <t>Mid-level</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Junior'}</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'lead'}</t>
+          <t>lead</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Lead'}</t>
+          <t>Lead</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'tech'}</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Tech'}</t>
+          <t>Tech</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
